--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-07T00:32:28+00:00</t>
+    <t>2024-10-29T05:47:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T05:47:19+00:00</t>
+    <t>2024-10-29T06:54:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T06:54:06+00:00</t>
+    <t>2024-10-29T07:29:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T07:29:07+00:00</t>
+    <t>2024-10-29T07:53:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T07:53:36+00:00</t>
+    <t>2024-10-29T08:28:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:28:36+00:00</t>
+    <t>2024-10-29T09:04:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:04:57+00:00</t>
+    <t>2024-10-29T09:10:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:10:27+00:00</t>
+    <t>2024-10-29T09:31:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
+++ b/jpcore-r4/feature/swg2_servicerequest/StructureDefinition-jp-immunization-certificateddate.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T09:31:27+00:00</t>
+    <t>2024-10-29T09:41:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
